--- a/Exam/gymtrackerpro/lib/repository/__tests__/bbt/user-repository/findMembers-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/repository/__tests__/bbt/user-repository/findMembers-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="121">
-  <si>
-    <t>Statement: UserRepository.findMembers(options?) – returns a paginated list of Members.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="92">
+  <si>
+    <t>Statement: UserRepository.findMembers(options?) – Returns a paginated list of members. Supports optional search filtering by name/email, pagination via page and pageSize, and results ordered by full name ascending.</t>
   </si>
   <si>
     <t/>
@@ -31,13 +31,13 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: MemberListOptions? { search?, page?, pageSize? }</t>
+    <t>Input: options?: MemberListOptions { search?: string, page?: number, pageSize?: number }</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>Database is accessible</t>
+    <t>Database is accessible. The member table may be empty or contain one or more records.</t>
   </si>
   <si>
     <t>Results</t>
@@ -49,7 +49,7 @@
     <t>postcondition</t>
   </si>
   <si>
-    <t>Returns filtered and paginated results ordered by fullName ASC.</t>
+    <t>On success: PageResult returned with items matching the filter, total reflecting the full count, and items ordered by user.fullName ascending.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,37 +64,28 @@
     <t>Invalid EC</t>
   </si>
   <si>
+    <t>Options</t>
+  </si>
+  <si>
+    <t>No options → default page returned, items.length: 1, total: 1</t>
+  </si>
+  <si>
     <t>Search filter</t>
   </si>
   <si>
-    <t>No search term</t>
-  </si>
-  <si>
-    <t>With search term</t>
+    <t>search: "John" → matching items returned, items.length: 1, total: 1</t>
   </si>
   <si>
     <t>Result ordering</t>
   </si>
   <si>
-    <t>Multiple members</t>
-  </si>
-  <si>
-    <t>Database state</t>
-  </si>
-  <si>
-    <t>Members exist</t>
-  </si>
-  <si>
-    <t>Empty database</t>
-  </si>
-  <si>
-    <t>Pagination</t>
-  </si>
-  <si>
-    <t>Default page/size</t>
-  </si>
-  <si>
-    <t>Custom page/size</t>
+    <t>Multiple members → items ordered by user.fullName ASC</t>
+  </si>
+  <si>
+    <t>Data availability</t>
+  </si>
+  <si>
+    <t>Empty database → items.length: 0, total: 0</t>
   </si>
   <si>
     <t>No TC</t>
@@ -112,13 +103,13 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>EC-1, EC-4, EC-6</t>
-  </si>
-  <si>
-    <t>No options, DB has members</t>
-  </si>
-  <si>
-    <t>Returns items and total</t>
+    <t>EC-1</t>
+  </si>
+  <si>
+    <t>no options</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 1, total: 1</t>
   </si>
   <si>
     <t>Passed</t>
@@ -127,34 +118,25 @@
     <t>EC-2</t>
   </si>
   <si>
-    <t>search="John"</t>
-  </si>
-  <si>
-    <t>Returns filtered results</t>
+    <t>options: { search: "John" }</t>
   </si>
   <si>
     <t>EC-3</t>
   </si>
   <si>
-    <t>Multiple results</t>
-  </si>
-  <si>
-    <t>Ordered by fullName ASC</t>
-  </si>
-  <si>
-    <t>EC-5</t>
-  </si>
-  <si>
-    <t>Returns items=[] total=0</t>
-  </si>
-  <si>
-    <t>EC-7</t>
-  </si>
-  <si>
-    <t>page=2, pageSize=10</t>
-  </si>
-  <si>
-    <t>Returns second page</t>
+    <t>no options, members: [memberAlice, MOCK_MEMBER_WITH_USER]</t>
+  </si>
+  <si>
+    <t>PageResult with items[0].user.fullName: "Alice Brown", items[1].user.fullName: "John Doe"</t>
+  </si>
+  <si>
+    <t>EC-4</t>
+  </si>
+  <si>
+    <t>no options, DB empty</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 0, total: 0</t>
   </si>
   <si>
     <t>Number BVA</t>
@@ -163,103 +145,97 @@
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>Search param</t>
-  </si>
-  <si>
-    <t>search = undefined</t>
-  </si>
-  <si>
-    <t>search = ""</t>
-  </si>
-  <si>
-    <t>search = "J"</t>
-  </si>
-  <si>
-    <t>Page param</t>
-  </si>
-  <si>
-    <t>page = undefined</t>
-  </si>
-  <si>
-    <t>page = 0</t>
-  </si>
-  <si>
-    <t>page = 1</t>
-  </si>
-  <si>
-    <t>page = 2</t>
-  </si>
-  <si>
-    <t>PageSize param</t>
-  </si>
-  <si>
-    <t>pageSize = undefined</t>
-  </si>
-  <si>
-    <t>pageSize = 0</t>
-  </si>
-  <si>
-    <t>pageSize = 1</t>
+    <t>Search value</t>
+  </si>
+  <si>
+    <t>search: undefined, search: "" (empty), search: "a" (one char)</t>
+  </si>
+  <si>
+    <t>Page number</t>
+  </si>
+  <si>
+    <t>page: undefined, page: 0 (first), page: 1 (first), page: 2 (second)</t>
+  </si>
+  <si>
+    <t>Page size</t>
+  </si>
+  <si>
+    <t>pageSize: undefined (default), pageSize: 0 (no items), pageSize: 1 (one item)</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>BVA-1 Undefined</t>
-  </si>
-  <si>
-    <t>Returns all members</t>
-  </si>
-  <si>
-    <t>BVA-2 Empty</t>
-  </si>
-  <si>
-    <t>BVA-3 OneChar</t>
-  </si>
-  <si>
-    <t>Returns matching members</t>
-  </si>
-  <si>
-    <t>BVA-4 Undefined</t>
-  </si>
-  <si>
-    <t>Defaults to page 1</t>
-  </si>
-  <si>
-    <t>BVA-5 Zero</t>
-  </si>
-  <si>
-    <t>BVA-6 One</t>
-  </si>
-  <si>
-    <t>Returns page 1</t>
-  </si>
-  <si>
-    <t>BVA-7 Two</t>
-  </si>
-  <si>
-    <t>page = 2, total=15</t>
-  </si>
-  <si>
-    <t>Returns page 2 (empty)</t>
-  </si>
-  <si>
-    <t>BVA-8 Undefined</t>
-  </si>
-  <si>
-    <t>Defaults to 10</t>
-  </si>
-  <si>
-    <t>BVA-9 Zero</t>
-  </si>
-  <si>
-    <t>Returns zero items</t>
-  </si>
-  <si>
-    <t>BVA-10 One</t>
-  </si>
-  <si>
-    <t>Returns one item</t>
+    <t>BVA-1 (undef)</t>
+  </si>
+  <si>
+    <t>options: { search: undefined }</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 1</t>
+  </si>
+  <si>
+    <t>BVA-1 (n=0)</t>
+  </si>
+  <si>
+    <t>options: { search: "" }</t>
+  </si>
+  <si>
+    <t>BVA-1 (n=1)</t>
+  </si>
+  <si>
+    <t>options: { search: "a" }</t>
+  </si>
+  <si>
+    <t>BVA-2 (undef)</t>
+  </si>
+  <si>
+    <t>options: { page: undefined }</t>
+  </si>
+  <si>
+    <t>BVA-2 (p=0)</t>
+  </si>
+  <si>
+    <t>options: { page: 0, pageSize: 10 }</t>
+  </si>
+  <si>
+    <t>BVA-2 (p=1)</t>
+  </si>
+  <si>
+    <t>options: { page: 1, pageSize: 10 }</t>
+  </si>
+  <si>
+    <t>BVA-2 (p=2)</t>
+  </si>
+  <si>
+    <t>options: { page: 2, pageSize: 10 }</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 0, total: 15</t>
+  </si>
+  <si>
+    <t>BVA-3 (undef)</t>
+  </si>
+  <si>
+    <t>options: { pageSize: undefined }</t>
+  </si>
+  <si>
+    <t>BVA-3 (s=0)</t>
+  </si>
+  <si>
+    <t>options: { pageSize: 0 }</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 0, total: 5</t>
+  </si>
+  <si>
+    <t>BVA-3 (s=1)</t>
+  </si>
+  <si>
+    <t>options: { pageSize: 1 }</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 1, total: 5</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -268,78 +244,15 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>EC-1</t>
-  </si>
-  <si>
-    <t>No options provided</t>
-  </si>
-  <si>
-    <t>Items length=1, total=1</t>
-  </si>
-  <si>
-    <t>Filtered items returned</t>
-  </si>
-  <si>
-    <t>Alice, John in DB</t>
-  </si>
-  <si>
-    <t>Alice comes before John</t>
-  </si>
-  <si>
-    <t>Empty DB</t>
-  </si>
-  <si>
-    <t>Items=[], total=0</t>
-  </si>
-  <si>
     <t>BVA-1</t>
   </si>
   <si>
-    <t>Returns items</t>
-  </si>
-  <si>
     <t>BVA-2</t>
   </si>
   <si>
     <t>BVA-3</t>
   </si>
   <si>
-    <t>BVA-4</t>
-  </si>
-  <si>
-    <t>Returns first page</t>
-  </si>
-  <si>
-    <t>BVA-5</t>
-  </si>
-  <si>
-    <t>BVA-6</t>
-  </si>
-  <si>
-    <t>BVA-7</t>
-  </si>
-  <si>
-    <t>page = 2, pageSize=10, total=15</t>
-  </si>
-  <si>
-    <t>Items length=0, total=15</t>
-  </si>
-  <si>
-    <t>BVA-8</t>
-  </si>
-  <si>
-    <t>BVA-9</t>
-  </si>
-  <si>
-    <t>Returns total but items=[]</t>
-  </si>
-  <si>
-    <t>BVA-10</t>
-  </si>
-  <si>
-    <t>Returns total and one item</t>
-  </si>
-  <si>
     <t>Testing</t>
   </si>
   <si>
@@ -370,7 +283,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>MEM-03</t>
+    <t>REPO-07</t>
   </si>
   <si>
     <t>n/a</t>
@@ -895,7 +808,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -936,10 +849,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>1</v>
@@ -950,10 +863,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>1</v>
@@ -964,55 +877,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1023,7 +894,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1035,19 +906,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1055,16 +926,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1072,16 +943,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1089,16 +960,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1106,33 +977,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1143,7 +997,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1153,13 +1007,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1167,10 +1021,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1178,10 +1032,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1189,87 +1043,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1292,19 +1069,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>29</v>
-      </c>
       <c r="E1" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1312,16 +1089,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1329,16 +1106,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1346,16 +1123,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="E4" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1363,16 +1140,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1380,16 +1157,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1397,16 +1174,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1414,16 +1191,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1431,16 +1208,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1448,16 +1225,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1465,16 +1242,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1498,22 +1275,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>29</v>
-      </c>
       <c r="F1" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1521,19 +1298,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1541,19 +1318,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>86</v>
+        <v>30</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1561,19 +1338,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>87</v>
+        <v>35</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>88</v>
+        <v>36</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1581,19 +1358,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1604,16 +1381,16 @@
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1624,16 +1401,16 @@
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1644,16 +1421,16 @@
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="F8" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1664,16 +1441,16 @@
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1684,16 +1461,16 @@
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1704,16 +1481,16 @@
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1724,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1744,16 +1521,16 @@
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1764,16 +1541,16 @@
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1784,16 +1561,16 @@
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1821,16 +1598,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1838,39 +1615,39 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>114</v>
+        <v>85</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B3" s="1">
         <v>14</v>
@@ -1885,19 +1662,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>120</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
